--- a/Audit_QMOD_SOP_Template.xlsx
+++ b/Audit_QMOD_SOP_Template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOP audit" sheetId="1" r:id="Re62f7a64208a4770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R48ff7f00a0114bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOP audit" sheetId="1" r:id="Re4f5fd1568024590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R3844b449e45146d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -39,13 +39,8 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="15"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -79,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -87,49 +82,40 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -334,650 +320,899 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>Audit QMOD – SOP Audit Template</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
+      <x:c r="G1" s="4"/>
+      <x:c r="H1" s="4"/>
+      <x:c r="I1" s="4"/>
+      <x:c r="J1" s="4"/>
+      <x:c r="K1" s="4"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>SOP Name</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" t="str">
         <x:v>QUALITY OF SERVICE NETWORK AUDIT STANDARD OPERATING PROCEDURE</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>SOP Code / Ref</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str"/>
+      <x:c r="B4" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>SOP Version / Revision</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str"/>
+      <x:c r="B5" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>Effective Date</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str"/>
+      <x:c r="B6" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="20" t="str">
+      <x:c r="A8" s="15" t="str">
+        <x:v>Item ID</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="B8" s="20" t="str">
+      <x:c r="C8" s="15" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="C8" s="20" t="str">
+      <x:c r="D8" s="15" t="str">
         <x:v>Audit Check</x:v>
       </x:c>
-      <x:c r="D8" s="20" t="str">
+      <x:c r="E8" s="15" t="str">
         <x:v>Evidence Expected</x:v>
       </x:c>
-      <x:c r="E8" s="20" t="str">
+      <x:c r="F8" s="15" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="str">
+        <x:v>Evidence Link / Reference</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="str">
+        <x:v>Auditor Remark</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="str">
+        <x:v>Remark</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="str">
         <x:v>Guidance / Notes</x:v>
       </x:c>
-      <x:c r="F8" s="20" t="str">
+      <x:c r="K8" s="15" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="n">
+      <x:c r="A9" t="str">
+        <x:v>SOP-001</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="str">
+      <x:c r="C9" s="20" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="str">
+      <x:c r="D9" s="20" t="str">
         <x:v>State Office has identified target locations / sites / areas for assessment</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="str">
+      <x:c r="E9" s="20" t="str">
         <x:v>Target list / planning document</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="str"/>
-      <x:c r="F9" t="str">
+      <x:c r="F9" s="20" t="str"/>
+      <x:c r="G9" s="20" t="str"/>
+      <x:c r="H9" s="20" t="str"/>
+      <x:c r="I9" s="20" t="str"/>
+      <x:c r="J9" s="20" t="str"/>
+      <x:c r="K9" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="n">
+      <x:c r="A10" t="str">
+        <x:v>SOP-002</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="str">
+      <x:c r="C10" s="20" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="str">
+      <x:c r="D10" s="20" t="str">
         <x:v>Officer in charge is clearly assigned</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="str">
+      <x:c r="E10" s="20" t="str">
         <x:v>Email assignment / task list</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="str"/>
-      <x:c r="F10" t="str">
+      <x:c r="F10" s="20" t="str"/>
+      <x:c r="G10" s="20" t="str"/>
+      <x:c r="H10" s="20" t="str"/>
+      <x:c r="I10" s="20" t="str"/>
+      <x:c r="J10" s="20" t="str"/>
+      <x:c r="K10" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="n">
+      <x:c r="A11" t="str">
+        <x:v>SOP-003</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B11" s="15" t="str">
+      <x:c r="C11" s="20" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="D11" s="20" t="str">
         <x:v>Scope of work is clearly defined before field activity</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
+      <x:c r="E11" s="20" t="str">
         <x:v>instruction email</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str"/>
-      <x:c r="F11" t="str">
+      <x:c r="F11" s="20" t="str"/>
+      <x:c r="G11" s="20" t="str"/>
+      <x:c r="H11" s="20" t="str"/>
+      <x:c r="I11" s="20" t="str"/>
+      <x:c r="J11" s="20" t="str"/>
+      <x:c r="K11" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="n">
+      <x:c r="A12" t="str">
+        <x:v>SOP-004</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B12" s="15" t="str">
+      <x:c r="C12" s="20" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="D12" s="20" t="str">
         <x:v>Required tools, devices or access are prepared before activity</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
+      <x:c r="E12" s="20" t="str">
         <x:v>Equipment checklist / system access record</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str"/>
-      <x:c r="F12" t="str">
+      <x:c r="F12" s="20" t="str"/>
+      <x:c r="G12" s="20" t="str"/>
+      <x:c r="H12" s="20" t="str"/>
+      <x:c r="I12" s="20" t="str"/>
+      <x:c r="J12" s="20" t="str"/>
+      <x:c r="K12" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="n">
+      <x:c r="A13" t="str">
+        <x:v>SOP-005</x:v>
+      </x:c>
+      <x:c r="B13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B13" s="15" t="str">
+      <x:c r="C13" s="20" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="D13" s="20" t="str">
         <x:v>Activity is carried out according to approved plan or instruction</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
+      <x:c r="E13" s="20" t="str">
         <x:v>Fieldwork record / log / photos</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str"/>
-      <x:c r="F13" t="str">
+      <x:c r="F13" s="20" t="str"/>
+      <x:c r="G13" s="20" t="str"/>
+      <x:c r="H13" s="20" t="str"/>
+      <x:c r="I13" s="20" t="str"/>
+      <x:c r="J13" s="20" t="str"/>
+      <x:c r="K13" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="n">
+      <x:c r="A14" t="str">
+        <x:v>SOP-006</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B14" s="15" t="str">
+      <x:c r="C14" s="20" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="D14" s="20" t="str">
         <x:v>Date, time, location and officer involved are recorded</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="str">
+      <x:c r="E14" s="20" t="str">
         <x:v>Attendance / site log / field form</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str"/>
-      <x:c r="F14" t="str">
+      <x:c r="F14" s="20" t="str"/>
+      <x:c r="G14" s="20" t="str"/>
+      <x:c r="H14" s="20" t="str"/>
+      <x:c r="I14" s="20" t="str"/>
+      <x:c r="J14" s="20" t="str"/>
+      <x:c r="K14" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="n">
+      <x:c r="A15" t="str">
+        <x:v>SOP-007</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B15" s="15" t="str">
+      <x:c r="C15" s="20" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="str">
+      <x:c r="D15" s="20" t="str">
         <x:v>Methodology used is consistent with SOP or technical requirement</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="str">
+      <x:c r="E15" s="20" t="str">
         <x:v>Test form / measurement setting / checklist</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str"/>
-      <x:c r="F15" t="str">
+      <x:c r="F15" s="20" t="str"/>
+      <x:c r="G15" s="20" t="str"/>
+      <x:c r="H15" s="20" t="str"/>
+      <x:c r="I15" s="20" t="str"/>
+      <x:c r="J15" s="20" t="str"/>
+      <x:c r="K15" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="n">
+      <x:c r="A16" t="str">
+        <x:v>SOP-008</x:v>
+      </x:c>
+      <x:c r="B16" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B16" s="15" t="str">
+      <x:c r="C16" s="20" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
+      <x:c r="D16" s="20" t="str">
         <x:v>Any issue during fieldwork is recorded</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="E16" s="20" t="str">
         <x:v>Issue log / email / field remarks</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str"/>
-      <x:c r="F16" t="str">
+      <x:c r="F16" s="20" t="str"/>
+      <x:c r="G16" s="20" t="str"/>
+      <x:c r="H16" s="20" t="str"/>
+      <x:c r="I16" s="20" t="str"/>
+      <x:c r="J16" s="20" t="str"/>
+      <x:c r="K16" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="n">
+      <x:c r="A17" t="str">
+        <x:v>SOP-009</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B17" s="15" t="str">
+      <x:c r="C17" s="20" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="str">
+      <x:c r="D17" s="20" t="str">
         <x:v>Any change from original plan is justified and approved</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="str">
+      <x:c r="E17" s="20" t="str">
         <x:v>Revised plan / approval email</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str"/>
-      <x:c r="F17" t="str">
+      <x:c r="F17" s="20" t="str"/>
+      <x:c r="G17" s="20" t="str"/>
+      <x:c r="H17" s="20" t="str"/>
+      <x:c r="I17" s="20" t="str"/>
+      <x:c r="J17" s="20" t="str"/>
+      <x:c r="K17" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="n">
+      <x:c r="A18" t="str">
+        <x:v>SOP-010</x:v>
+      </x:c>
+      <x:c r="B18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B18" s="15" t="str">
+      <x:c r="C18" s="20" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="str">
+      <x:c r="D18" s="20" t="str">
         <x:v>Required data fields are completely captured</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="str">
+      <x:c r="E18" s="20" t="str">
         <x:v>Completed data template / system record</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str"/>
-      <x:c r="F18" t="str">
+      <x:c r="F18" s="20" t="str"/>
+      <x:c r="G18" s="20" t="str"/>
+      <x:c r="H18" s="20" t="str"/>
+      <x:c r="I18" s="20" t="str"/>
+      <x:c r="J18" s="20" t="str"/>
+      <x:c r="K18" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="n">
+      <x:c r="A19" t="str">
+        <x:v>SOP-011</x:v>
+      </x:c>
+      <x:c r="B19" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B19" s="15" t="str">
+      <x:c r="C19" s="20" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="str">
+      <x:c r="D19" s="20" t="str">
         <x:v>Data is checked for completeness before analysis</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="str">
+      <x:c r="E19" s="20" t="str">
         <x:v>QC checklist / review notes</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str"/>
-      <x:c r="F19" t="str">
+      <x:c r="F19" s="20" t="str"/>
+      <x:c r="G19" s="20" t="str"/>
+      <x:c r="H19" s="20" t="str"/>
+      <x:c r="I19" s="20" t="str"/>
+      <x:c r="J19" s="20" t="str"/>
+      <x:c r="K19" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="n">
+      <x:c r="A20" t="str">
+        <x:v>SOP-012</x:v>
+      </x:c>
+      <x:c r="B20" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B20" s="15" t="str">
+      <x:c r="C20" s="20" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="D20" s="20" t="str">
         <x:v>Abnormal, missing or inconsistent data is flagged</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="E20" s="20" t="str">
         <x:v>Exception log / remarks</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str"/>
-      <x:c r="F20" t="str">
+      <x:c r="F20" s="20" t="str"/>
+      <x:c r="G20" s="20" t="str"/>
+      <x:c r="H20" s="20" t="str"/>
+      <x:c r="I20" s="20" t="str"/>
+      <x:c r="J20" s="20" t="str"/>
+      <x:c r="K20" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="n">
+      <x:c r="A21" t="str">
+        <x:v>SOP-013</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B21" s="15" t="str">
+      <x:c r="C21" s="20" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="str">
+      <x:c r="D21" s="20" t="str">
         <x:v>Data is stored in official location</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="str">
+      <x:c r="E21" s="20" t="str">
         <x:v>SharePoint / system / shared drive</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str"/>
-      <x:c r="F21" t="str">
+      <x:c r="F21" s="20" t="str"/>
+      <x:c r="G21" s="20" t="str"/>
+      <x:c r="H21" s="20" t="str"/>
+      <x:c r="I21" s="20" t="str"/>
+      <x:c r="J21" s="20" t="str"/>
+      <x:c r="K21" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="n">
+      <x:c r="A22" t="str">
+        <x:v>SOP-014</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B22" s="15" t="str">
+      <x:c r="C22" s="20" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="D22" s="20" t="str">
         <x:v>Collected data is analysed according to required method</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="str">
+      <x:c r="E22" s="20" t="str">
         <x:v>Analysis file / calculation sheet / dashboard</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str"/>
-      <x:c r="F22" t="str">
+      <x:c r="F22" s="20" t="str"/>
+      <x:c r="G22" s="20" t="str"/>
+      <x:c r="H22" s="20" t="str"/>
+      <x:c r="I22" s="20" t="str"/>
+      <x:c r="J22" s="20" t="str"/>
+      <x:c r="K22" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" t="n">
+      <x:c r="A23" t="str">
+        <x:v>SOP-015</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B23" s="15" t="str">
+      <x:c r="C23" s="20" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="str">
+      <x:c r="D23" s="20" t="str">
         <x:v>Result is reviewed before reporting</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="str">
+      <x:c r="E23" s="20" t="str">
         <x:v>Review email / sign-off</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str"/>
-      <x:c r="F23" t="str">
+      <x:c r="F23" s="20" t="str"/>
+      <x:c r="G23" s="20" t="str"/>
+      <x:c r="H23" s="20" t="str"/>
+      <x:c r="I23" s="20" t="str"/>
+      <x:c r="J23" s="20" t="str"/>
+      <x:c r="K23" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="n">
+      <x:c r="A24" t="str">
+        <x:v>SOP-016</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B24" s="15" t="str">
+      <x:c r="C24" s="20" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="D24" s="20" t="str">
         <x:v>Failed / non-compliant result is properly identified</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="str">
+      <x:c r="E24" s="20" t="str">
         <x:v>Non-compliance list / finding summary (including FIR)</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str"/>
-      <x:c r="F24" t="str">
+      <x:c r="F24" s="20" t="str"/>
+      <x:c r="G24" s="20" t="str"/>
+      <x:c r="H24" s="20" t="str"/>
+      <x:c r="I24" s="20" t="str"/>
+      <x:c r="J24" s="20" t="str"/>
+      <x:c r="K24" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" t="n">
+      <x:c r="A25" t="str">
+        <x:v>SOP-017</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B25" s="15" t="str">
+      <x:c r="C25" s="20" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="str">
+      <x:c r="D25" s="20" t="str">
         <x:v>Supporting evidence matches the reported result</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="str">
+      <x:c r="E25" s="20" t="str">
         <x:v>Raw data vs report sample</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str"/>
-      <x:c r="F25" t="str">
+      <x:c r="F25" s="20" t="str"/>
+      <x:c r="G25" s="20" t="str"/>
+      <x:c r="H25" s="20" t="str"/>
+      <x:c r="I25" s="20" t="str"/>
+      <x:c r="J25" s="20" t="str"/>
+      <x:c r="K25" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="n">
+      <x:c r="A26" t="str">
+        <x:v>SOP-018</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B26" s="15" t="str">
+      <x:c r="C26" s="20" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="str">
+      <x:c r="D26" s="20" t="str">
         <x:v>Any assumptions or exclusions are documented</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="str">
+      <x:c r="E26" s="20" t="str">
         <x:v>Analysis note / justification</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str"/>
-      <x:c r="F26" t="str">
+      <x:c r="F26" s="20" t="str"/>
+      <x:c r="G26" s="20" t="str"/>
+      <x:c r="H26" s="20" t="str"/>
+      <x:c r="I26" s="20" t="str"/>
+      <x:c r="J26" s="20" t="str"/>
+      <x:c r="K26" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" t="n">
+      <x:c r="A27" t="str">
+        <x:v>SOP-019</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B27" s="15" t="str">
+      <x:c r="C27" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="str">
+      <x:c r="D27" s="20" t="str">
         <x:v>Measurement results are entered into the Tracker</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="str">
+      <x:c r="E27" s="20" t="str">
         <x:v>Tracker</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str"/>
-      <x:c r="F27" t="str">
+      <x:c r="F27" s="20" t="str"/>
+      <x:c r="G27" s="20" t="str"/>
+      <x:c r="H27" s="20" t="str"/>
+      <x:c r="I27" s="20" t="str"/>
+      <x:c r="J27" s="20" t="str"/>
+      <x:c r="K27" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" t="n">
+      <x:c r="A28" t="str">
+        <x:v>SOP-020</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B28" s="15" t="str">
+      <x:c r="C28" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="str">
+      <x:c r="D28" s="20" t="str">
         <x:v>All mandatory fields in the tracker are completed</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="str">
+      <x:c r="E28" s="20" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str"/>
-      <x:c r="F28" t="str">
+      <x:c r="F28" s="20" t="str"/>
+      <x:c r="G28" s="20" t="str"/>
+      <x:c r="H28" s="20" t="str"/>
+      <x:c r="I28" s="20" t="str"/>
+      <x:c r="J28" s="20" t="str"/>
+      <x:c r="K28" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="n">
+      <x:c r="A29" t="str">
+        <x:v>SOP-021</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B29" s="15" t="str">
+      <x:c r="C29" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="str">
+      <x:c r="D29" s="20" t="str">
         <x:v>Operator / Service Provider information is correctly selected or entered</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="str">
+      <x:c r="E29" s="20" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str"/>
-      <x:c r="F29" t="str">
+      <x:c r="F29" s="20" t="str"/>
+      <x:c r="G29" s="20" t="str"/>
+      <x:c r="H29" s="20" t="str"/>
+      <x:c r="I29" s="20" t="str"/>
+      <x:c r="J29" s="20" t="str"/>
+      <x:c r="K29" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="n">
+      <x:c r="A30" t="str">
+        <x:v>SOP-022</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B30" s="15" t="str">
+      <x:c r="C30" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="str">
+      <x:c r="D30" s="20" t="str">
         <x:v>Required measurement indicators are completely filled in</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="str">
+      <x:c r="E30" s="20" t="str">
         <x:v>Tracker</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str"/>
-      <x:c r="F30" t="str">
+      <x:c r="F30" s="20" t="str"/>
+      <x:c r="G30" s="20" t="str"/>
+      <x:c r="H30" s="20" t="str"/>
+      <x:c r="I30" s="20" t="str"/>
+      <x:c r="J30" s="20" t="str"/>
+      <x:c r="K30" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="n">
+      <x:c r="A31" t="str">
+        <x:v>SOP-023</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B31" s="15" t="str">
+      <x:c r="C31" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="str">
+      <x:c r="D31" s="20" t="str">
         <x:v>Tracker format or template is not altered without approval</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="str">
+      <x:c r="E31" s="20" t="str">
         <x:v>Tracker</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str"/>
-      <x:c r="F31" t="str">
+      <x:c r="F31" s="20" t="str"/>
+      <x:c r="G31" s="20" t="str"/>
+      <x:c r="H31" s="20" t="str"/>
+      <x:c r="I31" s="20" t="str"/>
+      <x:c r="J31" s="20" t="str"/>
+      <x:c r="K31" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="n">
+      <x:c r="A32" t="str">
+        <x:v>SOP-024</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B32" s="15" t="str">
+      <x:c r="C32" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="str">
+      <x:c r="D32" s="20" t="str">
         <x:v>Data entered in the tracker is consistent with source/raw measurement records</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="str">
+      <x:c r="E32" s="20" t="str">
         <x:v>Raw data /measurement log</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str"/>
-      <x:c r="F32" t="str">
+      <x:c r="F32" s="20" t="str"/>
+      <x:c r="G32" s="20" t="str"/>
+      <x:c r="H32" s="20" t="str"/>
+      <x:c r="I32" s="20" t="str"/>
+      <x:c r="J32" s="20" t="str"/>
+      <x:c r="K32" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" t="n">
+      <x:c r="A33" t="str">
+        <x:v>SOP-025</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B33" s="15" t="str">
+      <x:c r="C33" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="str">
+      <x:c r="D33" s="20" t="str">
         <x:v>Incomplete, abnormal or missing data is clearly marked with remarks or justification</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="str">
+      <x:c r="E33" s="20" t="str">
         <x:v>Tracker remarks column</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str"/>
-      <x:c r="F33" t="str">
+      <x:c r="F33" s="20" t="str"/>
+      <x:c r="G33" s="20" t="str"/>
+      <x:c r="H33" s="20" t="str"/>
+      <x:c r="I33" s="20" t="str"/>
+      <x:c r="J33" s="20" t="str"/>
+      <x:c r="K33" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" t="n">
+      <x:c r="A34" t="str">
+        <x:v>SOP-026</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B34" s="15" t="str">
+      <x:c r="C34" s="20" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="str">
+      <x:c r="D34" s="20" t="str">
         <x:v>Tracker is updated within the required timeline</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="str">
+      <x:c r="E34" s="20" t="str">
         <x:v>File modified date / submission email / SharePoint timestamp</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str"/>
-      <x:c r="F34" t="str">
+      <x:c r="F34" s="20" t="str"/>
+      <x:c r="G34" s="20" t="str"/>
+      <x:c r="H34" s="20" t="str"/>
+      <x:c r="I34" s="20" t="str"/>
+      <x:c r="J34" s="20" t="str"/>
+      <x:c r="K34" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" t="n">
+      <x:c r="A35" t="str">
+        <x:v>SOP-027</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B35" s="15" t="str">
+      <x:c r="C35" s="20" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="str">
+      <x:c r="D35" s="20" t="str">
         <x:v>Issues requiring follow-up are recorded</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="str">
+      <x:c r="E35" s="20" t="str">
         <x:v>Follow-up tracker</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="str"/>
-      <x:c r="F35" t="str">
+      <x:c r="F35" s="20" t="str"/>
+      <x:c r="G35" s="20" t="str"/>
+      <x:c r="H35" s="20" t="str"/>
+      <x:c r="I35" s="20" t="str"/>
+      <x:c r="J35" s="20" t="str"/>
+      <x:c r="K35" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" t="n">
+      <x:c r="A36" t="str">
+        <x:v>SOP-028</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B36" s="15" t="str">
+      <x:c r="C36" s="20" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="str">
+      <x:c r="D36" s="20" t="str">
         <x:v>Service Provider is notified where applicable</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="str">
+      <x:c r="E36" s="20" t="str">
         <x:v>Letter / email</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="str"/>
-      <x:c r="F36" t="str">
+      <x:c r="F36" s="20" t="str"/>
+      <x:c r="G36" s="20" t="str"/>
+      <x:c r="H36" s="20" t="str"/>
+      <x:c r="I36" s="20" t="str"/>
+      <x:c r="J36" s="20" t="str"/>
+      <x:c r="K36" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" t="n">
+      <x:c r="A37" t="str">
+        <x:v>SOP-029</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B37" s="15" t="str">
+      <x:c r="C37" s="20" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="str">
+      <x:c r="D37" s="20" t="str">
         <x:v>Reminder is issued if there is no response</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="str">
+      <x:c r="E37" s="20" t="str">
         <x:v>Reminder email</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="str"/>
-      <x:c r="F37" t="str">
+      <x:c r="F37" s="20" t="str"/>
+      <x:c r="G37" s="20" t="str"/>
+      <x:c r="H37" s="20" t="str"/>
+      <x:c r="I37" s="20" t="str"/>
+      <x:c r="J37" s="20" t="str"/>
+      <x:c r="K37" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" t="n">
+      <x:c r="A38" t="str">
+        <x:v>SOP-030</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B38" s="15" t="str">
+      <x:c r="C38" s="20" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="D38" s="20" t="str">
         <x:v>Escalation is made for overdue or serious issues</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="str">
+      <x:c r="E38" s="20" t="str">
         <x:v>Escalation email / management update</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="str"/>
-      <x:c r="F38" t="str">
+      <x:c r="F38" s="20" t="str"/>
+      <x:c r="G38" s="20" t="str"/>
+      <x:c r="H38" s="20" t="str"/>
+      <x:c r="I38" s="20" t="str"/>
+      <x:c r="J38" s="20" t="str"/>
+      <x:c r="K38" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" t="n">
+      <x:c r="A39" t="str">
+        <x:v>SOP-031</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B39" s="15" t="str">
+      <x:c r="C39" s="20" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="str">
+      <x:c r="D39" s="20" t="str">
         <x:v>Case is closed only when required evidence is complete</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="str">
+      <x:c r="E39" s="20" t="str">
         <x:v>Closure note / final evidence</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="str"/>
-      <x:c r="F39" t="str">
+      <x:c r="F39" s="20" t="str"/>
+      <x:c r="G39" s="20" t="str"/>
+      <x:c r="H39" s="20" t="str"/>
+      <x:c r="I39" s="20" t="str"/>
+      <x:c r="J39" s="20" t="str"/>
+      <x:c r="K39" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" t="n">
+      <x:c r="A40" t="str">
+        <x:v>SOP-032</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B40" s="15" t="str">
+      <x:c r="C40" s="20" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="str">
+      <x:c r="D40" s="20" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="str"/>
-      <x:c r="E40" s="15" t="str"/>
-      <x:c r="F40" t="str">
+      <x:c r="E40" s="20" t="str"/>
+      <x:c r="F40" s="20" t="str"/>
+      <x:c r="G40" s="20" t="str"/>
+      <x:c r="H40" s="20" t="str"/>
+      <x:c r="I40" s="20" t="str"/>
+      <x:c r="J40" s="20" t="str"/>
+      <x:c r="K40" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:K1"/>
   </x:mergeCells>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F9:F40">
+    <x:dataValidation type="list" sqref="K9:K40">
       <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -990,111 +1225,86 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="25" t="str">
-        <x:v>How to create a new SOP template for Audit QMOD</x:v>
-      </x:c>
-      <x:c r="B1" s="25"/>
-      <x:c r="C1" s="25"/>
-      <x:c r="D1" s="25"/>
-      <x:c r="E1" s="25"/>
+      <x:c r="A1" s="24" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>What to do</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>Important</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>Save a copy and rename it for the new SOP.</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>Keep the 'SOP audit' worksheet name for local import.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="29" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B3" s="29" t="str">
-        <x:v>What to do</x:v>
-      </x:c>
-      <x:c r="C3" s="29" t="str">
-        <x:v>Important</x:v>
+      <x:c r="A3" s="20" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>Change SOP Name and edit Section / Audit Check / Evidence Expected.</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>Evidence Expected is shown prominently to the auditor.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="15" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>Save a copy of this workbook and rename it for the new SOP.</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="str">
-        <x:v>Do not rename the 'SOP audit' worksheet.</x:v>
+      <x:c r="A4" s="20" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>Leave Status, Evidence Link / Reference, Auditor Remark and Remark blank.</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>These are audit response fields stored by the app during the actual audit.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="15" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="15" t="str">
-        <x:v>Change SOP Name in cell B3. SOP Code / Ref, Version and Effective Date are optional.</x:v>
-      </x:c>
-      <x:c r="C5" s="15" t="str">
-        <x:v>SOP Name is used as the name shown inside Audit QMOD.</x:v>
+      <x:c r="A5" s="20" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>Keep existing Item IDs for wording changes; create new IDs for new requirements.</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>This protects existing responses when a template is updated.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="15" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="15" t="str">
-        <x:v>Edit the checklist from row 9 downward.</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="str">
-        <x:v>Each active row needs Section and Audit Check.</x:v>
+      <x:c r="A6" s="20" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>Set Active = No for rows the app should ignore.</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>You can also delete unused rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="15" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="15" t="str">
-        <x:v>Set Active = No for rows you want the app to ignore.</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="str">
-        <x:v>You can also delete unused rows.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="15" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>Keep Evidence Expected short and practical.</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="str">
-        <x:v>It will be displayed to the auditor under each check.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="15" t="str">
+      <x:c r="A7" s="20" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="str">
-        <x:v>In Audit QMOD, open SOP Audit → Manage SOP Templates → Import SOP Template.</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="str">
-        <x:v>The app stores the imported template offline on that device.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="15" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>Existing audits keep their own checklist snapshot.</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="str">
-        <x:v>Replacing a template later will not change old audit records.</x:v>
-      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>Import via Audit Templates for testing, or add the SOP sheet to the repository master workbook for all users.</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>